--- a/artfynd/A 34207-2022 artfynd.xlsx
+++ b/artfynd/A 34207-2022 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123962228</v>
+        <v>123962224</v>
       </c>
       <c r="B3" t="n">
-        <v>58200</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103057</v>
+        <v>100082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,14 +834,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123962224</v>
+        <v>123962228</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>58200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,20 +935,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100082</v>
+        <v>103057</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,14 +958,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>

--- a/artfynd/A 34207-2022 artfynd.xlsx
+++ b/artfynd/A 34207-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123962225</v>
+        <v>123962224</v>
       </c>
       <c r="B2" t="n">
-        <v>57670</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102623</v>
+        <v>100082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123962224</v>
+        <v>123962228</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>58200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100082</v>
+        <v>103057</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,14 +834,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123962228</v>
+        <v>123962225</v>
       </c>
       <c r="B4" t="n">
-        <v>58200</v>
+        <v>57670</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,20 +935,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103057</v>
+        <v>102623</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,14 +958,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>

--- a/artfynd/A 34207-2022 artfynd.xlsx
+++ b/artfynd/A 34207-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123962224</v>
+        <v>123962228</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>58200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100082</v>
+        <v>103057</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,14 +710,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123962228</v>
+        <v>123962224</v>
       </c>
       <c r="B3" t="n">
-        <v>58200</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103057</v>
+        <v>100082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,14 +834,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>

--- a/artfynd/A 34207-2022 artfynd.xlsx
+++ b/artfynd/A 34207-2022 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123962224</v>
+        <v>123962225</v>
       </c>
       <c r="B3" t="n">
-        <v>57421</v>
+        <v>57692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100082</v>
+        <v>102623</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,7 +841,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123962225</v>
+        <v>123962224</v>
       </c>
       <c r="B4" t="n">
-        <v>57692</v>
+        <v>57421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102623</v>
+        <v>100082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -965,7 +965,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>

--- a/artfynd/A 34207-2022 artfynd.xlsx
+++ b/artfynd/A 34207-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123962228</v>
+        <v>123962224</v>
       </c>
       <c r="B2" t="n">
-        <v>58222</v>
+        <v>57421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103057</v>
+        <v>100082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,14 +710,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123962225</v>
+        <v>123962228</v>
       </c>
       <c r="B3" t="n">
-        <v>57692</v>
+        <v>58222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102623</v>
+        <v>103057</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,14 +834,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123962224</v>
+        <v>123962225</v>
       </c>
       <c r="B4" t="n">
-        <v>57421</v>
+        <v>57692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100082</v>
+        <v>102623</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -965,7 +965,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>

--- a/artfynd/A 34207-2022 artfynd.xlsx
+++ b/artfynd/A 34207-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123962224</v>
+        <v>123962228</v>
       </c>
       <c r="B2" t="n">
-        <v>57421</v>
+        <v>58222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100082</v>
+        <v>103057</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,14 +710,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123962228</v>
+        <v>123962224</v>
       </c>
       <c r="B3" t="n">
-        <v>58222</v>
+        <v>57421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103057</v>
+        <v>100082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,14 +834,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>

--- a/artfynd/A 34207-2022 artfynd.xlsx
+++ b/artfynd/A 34207-2022 artfynd.xlsx
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123962228</v>
+        <v>123962224</v>
       </c>
       <c r="B2" t="n">
-        <v>58222</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103057</v>
+        <v>100082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,14 +705,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -799,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123962224</v>
+        <v>123962225</v>
       </c>
       <c r="B3" t="n">
-        <v>57421</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100082</v>
+        <v>102623</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,7 +831,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -923,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123962225</v>
+        <v>123962228</v>
       </c>
       <c r="B4" t="n">
-        <v>57692</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102623</v>
+        <v>103057</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,14 +943,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>

--- a/artfynd/A 34207-2022 artfynd.xlsx
+++ b/artfynd/A 34207-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123962224</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123962225</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,8 +1044,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123962228</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>